--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/158.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/158.xlsx
@@ -426,13 +426,13 @@
         <v>-7.999356276417432</v>
       </c>
       <c r="E2">
-        <v>-8.237450264776243</v>
+        <v>-9.279809883387799</v>
       </c>
       <c r="F2">
-        <v>-3.280890547720165</v>
+        <v>-3.788984581746941</v>
       </c>
       <c r="G2">
-        <v>-7.355063349085905</v>
+        <v>-7.316051880451133</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.749493993179775</v>
       </c>
       <c r="E3">
-        <v>-9.168010917086432</v>
+        <v>-9.325728609825575</v>
       </c>
       <c r="F3">
-        <v>-3.091461899468537</v>
+        <v>-3.792748258854983</v>
       </c>
       <c r="G3">
-        <v>-6.895834403514824</v>
+        <v>-6.560257644381061</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.434082674444494</v>
       </c>
       <c r="E4">
-        <v>-9.482531550815169</v>
+        <v>-9.076019496094617</v>
       </c>
       <c r="F4">
-        <v>-3.158601528047677</v>
+        <v>-3.814316749717352</v>
       </c>
       <c r="G4">
-        <v>-7.22576668250413</v>
+        <v>-6.645517434199451</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.055026777381899</v>
       </c>
       <c r="E5">
-        <v>-10.15945690242975</v>
+        <v>-10.67302208269163</v>
       </c>
       <c r="F5">
-        <v>-3.358849263260629</v>
+        <v>-3.778215381521953</v>
       </c>
       <c r="G5">
-        <v>-6.646222580399316</v>
+        <v>-7.161508993586875</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.585970279171926</v>
       </c>
       <c r="E6">
-        <v>-10.44400809517572</v>
+        <v>-10.77221377735564</v>
       </c>
       <c r="F6">
-        <v>-3.113375638220472</v>
+        <v>-3.68945975090298</v>
       </c>
       <c r="G6">
-        <v>-6.026644051088095</v>
+        <v>-6.439339968559181</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.009124345524529</v>
       </c>
       <c r="E7">
-        <v>-12.06389306093349</v>
+        <v>-11.09635741835068</v>
       </c>
       <c r="F7">
-        <v>-3.201398804853555</v>
+        <v>-3.552192040682265</v>
       </c>
       <c r="G7">
-        <v>-6.59669019804074</v>
+        <v>-6.619582620444801</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.317915703399272</v>
       </c>
       <c r="E8">
-        <v>-11.89480436996109</v>
+        <v>-11.76408091078167</v>
       </c>
       <c r="F8">
-        <v>-3.096848875139904</v>
+        <v>-4.057777484538986</v>
       </c>
       <c r="G8">
-        <v>-5.710430672813529</v>
+        <v>-6.395677183441733</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.512440782269919</v>
       </c>
       <c r="E9">
-        <v>-12.99115245569209</v>
+        <v>-13.64371914561941</v>
       </c>
       <c r="F9">
-        <v>-3.19301070647243</v>
+        <v>-3.74221932976993</v>
       </c>
       <c r="G9">
-        <v>-4.78482531385208</v>
+        <v>-5.846941018125377</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.616774744915243</v>
       </c>
       <c r="E10">
-        <v>-14.03988816570645</v>
+        <v>-13.38289715667363</v>
       </c>
       <c r="F10">
-        <v>-2.932895720244035</v>
+        <v>-3.760020184259469</v>
       </c>
       <c r="G10">
-        <v>-4.763313388937896</v>
+        <v>-4.999292385522685</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.658261114680755</v>
       </c>
       <c r="E11">
-        <v>-14.00872773605967</v>
+        <v>-14.66023023459519</v>
       </c>
       <c r="F11">
-        <v>-2.937051364566149</v>
+        <v>-4.000756153053588</v>
       </c>
       <c r="G11">
-        <v>-4.306097255054691</v>
+        <v>-4.872650776463406</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.687535390894546</v>
       </c>
       <c r="E12">
-        <v>-14.6482524208449</v>
+        <v>-14.97487766559614</v>
       </c>
       <c r="F12">
-        <v>-2.618586317589303</v>
+        <v>-3.465682105051386</v>
       </c>
       <c r="G12">
-        <v>-4.130836974205675</v>
+        <v>-3.788036604705222</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.7489209997443992</v>
       </c>
       <c r="E13">
-        <v>-15.19520151149132</v>
+        <v>-15.63170564956468</v>
       </c>
       <c r="F13">
-        <v>-2.732579093823762</v>
+        <v>-3.300024882590504</v>
       </c>
       <c r="G13">
-        <v>-2.825174366244815</v>
+        <v>-3.976886674992947</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.09987449183824999</v>
       </c>
       <c r="E14">
-        <v>-15.0311167842974</v>
+        <v>-16.16199448433689</v>
       </c>
       <c r="F14">
-        <v>-2.802920183910962</v>
+        <v>-2.970366202203333</v>
       </c>
       <c r="G14">
-        <v>-1.719730241953537</v>
+        <v>-3.334521660734923</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.8168675688589158</v>
       </c>
       <c r="E15">
-        <v>-16.68595704092037</v>
+        <v>-15.91494358484843</v>
       </c>
       <c r="F15">
-        <v>-2.524004232907429</v>
+        <v>-3.204793478483299</v>
       </c>
       <c r="G15">
-        <v>-2.441528485880834</v>
+        <v>-2.11536029716968</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.362418591030981</v>
       </c>
       <c r="E16">
-        <v>-16.71307807175231</v>
+        <v>-17.20020602075741</v>
       </c>
       <c r="F16">
-        <v>-2.187351115344719</v>
+        <v>-3.043474026524806</v>
       </c>
       <c r="G16">
-        <v>-1.387222358534679</v>
+        <v>-2.268552481453915</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.714497948470539</v>
       </c>
       <c r="E17">
-        <v>-18.6457583226419</v>
+        <v>-17.69432593363036</v>
       </c>
       <c r="F17">
-        <v>-2.132362470401788</v>
+        <v>-2.567557729287929</v>
       </c>
       <c r="G17">
-        <v>-0.7743940315780322</v>
+        <v>-0.9284337155203205</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.85867912606955</v>
       </c>
       <c r="E18">
-        <v>-19.55354075069351</v>
+        <v>-19.64767413989095</v>
       </c>
       <c r="F18">
-        <v>-1.930141437618198</v>
+        <v>-2.149369888227692</v>
       </c>
       <c r="G18">
-        <v>-0.1993721346798626</v>
+        <v>-1.181137588169508</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.794640350683519</v>
       </c>
       <c r="E19">
-        <v>-20.28878379057887</v>
+        <v>-20.2837254851123</v>
       </c>
       <c r="F19">
-        <v>-1.684489645662555</v>
+        <v>-2.254968231257364</v>
       </c>
       <c r="G19">
-        <v>0.3214693739225947</v>
+        <v>-1.385792202861714</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.527822114796764</v>
       </c>
       <c r="E20">
-        <v>-20.46180319698993</v>
+        <v>-20.67522564849742</v>
       </c>
       <c r="F20">
-        <v>-1.157088652820656</v>
+        <v>-1.661469688328685</v>
       </c>
       <c r="G20">
-        <v>-0.3988920932406585</v>
+        <v>-0.5887551904634004</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.07702389550717</v>
       </c>
       <c r="E21">
-        <v>-20.63908842591621</v>
+        <v>-21.68633426798205</v>
       </c>
       <c r="F21">
-        <v>-1.035532888987017</v>
+        <v>-1.660853626727579</v>
       </c>
       <c r="G21">
-        <v>-0.2998405707056646</v>
+        <v>-0.4519601382351757</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.4626503167347553</v>
       </c>
       <c r="E22">
-        <v>-23.10586595821846</v>
+        <v>-21.62510024245033</v>
       </c>
       <c r="F22">
-        <v>-0.7613047074931839</v>
+        <v>-1.270998284494554</v>
       </c>
       <c r="G22">
-        <v>0.2041370189197453</v>
+        <v>0.02793323259203636</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.2811970234332539</v>
       </c>
       <c r="E23">
-        <v>-22.84837239766831</v>
+        <v>-22.18401356142502</v>
       </c>
       <c r="F23">
-        <v>-0.342468338860575</v>
+        <v>-1.12264938398351</v>
       </c>
       <c r="G23">
-        <v>-0.3871860042137956</v>
+        <v>-1.32911897377493</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.123961821720427</v>
       </c>
       <c r="E24">
-        <v>-22.871214020563</v>
+        <v>-23.01903699759539</v>
       </c>
       <c r="F24">
-        <v>-0.5220669244950701</v>
+        <v>-1.045840438937655</v>
       </c>
       <c r="G24">
-        <v>0.062134478558247</v>
+        <v>-1.185305565003451</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.022573221204321</v>
       </c>
       <c r="E25">
-        <v>-23.37099905441954</v>
+        <v>-23.90328494622913</v>
       </c>
       <c r="F25">
-        <v>-0.490206720741217</v>
+        <v>-0.9742505967361297</v>
       </c>
       <c r="G25">
-        <v>-0.2798382545573881</v>
+        <v>-1.151534689957345</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.941661081753513</v>
       </c>
       <c r="E26">
-        <v>-23.27859101381902</v>
+        <v>-22.74339784169651</v>
       </c>
       <c r="F26">
-        <v>-0.5165477093797636</v>
+        <v>-1.157609692066836</v>
       </c>
       <c r="G26">
-        <v>-0.9536501408929492</v>
+        <v>-1.211422458762761</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.838407667706549</v>
       </c>
       <c r="E27">
-        <v>-23.38286818479365</v>
+        <v>-23.01074536168734</v>
       </c>
       <c r="F27">
-        <v>-0.401699731950968</v>
+        <v>-1.024416857166547</v>
       </c>
       <c r="G27">
-        <v>-0.7915128625616035</v>
+        <v>-1.884903290544395</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.679668977371263</v>
       </c>
       <c r="E28">
-        <v>-23.07120954663776</v>
+        <v>-23.79484157916745</v>
       </c>
       <c r="F28">
-        <v>-0.4941145150875638</v>
+        <v>-1.051652639647317</v>
       </c>
       <c r="G28">
-        <v>-1.219298246600687</v>
+        <v>-1.447149853886566</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.428612554680571</v>
       </c>
       <c r="E29">
-        <v>-22.75751309517842</v>
+        <v>-24.27717387419843</v>
       </c>
       <c r="F29">
-        <v>-0.160315235584476</v>
+        <v>-1.104998981555937</v>
       </c>
       <c r="G29">
-        <v>-1.079563429933589</v>
+        <v>-1.723699586055124</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.058703547626819</v>
       </c>
       <c r="E30">
-        <v>-22.77612059487593</v>
+        <v>-23.39225118293754</v>
       </c>
       <c r="F30">
-        <v>-0.6262320136712688</v>
+        <v>-1.305995017813935</v>
       </c>
       <c r="G30">
-        <v>-1.38617291559873</v>
+        <v>-2.032487410685104</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.548966949737197</v>
       </c>
       <c r="E31">
-        <v>-22.27630839017535</v>
+        <v>-23.1622137602959</v>
       </c>
       <c r="F31">
-        <v>-0.486943494702454</v>
+        <v>-1.396446797468343</v>
       </c>
       <c r="G31">
-        <v>-1.626677427935703</v>
+        <v>-1.598428542849102</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.889921150124072</v>
       </c>
       <c r="E32">
-        <v>-21.56649273184306</v>
+        <v>-21.64291073072249</v>
       </c>
       <c r="F32">
-        <v>-0.6478678120350448</v>
+        <v>-1.087164869242174</v>
       </c>
       <c r="G32">
-        <v>-1.888654138640389</v>
+        <v>-1.505143990643518</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.085406686809398</v>
       </c>
       <c r="E33">
-        <v>-21.56392508708071</v>
+        <v>-22.06893145146809</v>
       </c>
       <c r="F33">
-        <v>-0.6137009406153542</v>
+        <v>-1.269677473761077</v>
       </c>
       <c r="G33">
-        <v>-2.03041831972306</v>
+        <v>-1.455932731202252</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.147374174554872</v>
       </c>
       <c r="E34">
-        <v>-21.72709506252509</v>
+        <v>-22.61145169453502</v>
       </c>
       <c r="F34">
-        <v>-0.7426098510143789</v>
+        <v>-1.59907880193699</v>
       </c>
       <c r="G34">
-        <v>-1.53970608607351</v>
+        <v>-1.771308541455383</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.101137003901502</v>
       </c>
       <c r="E35">
-        <v>-20.74238291803118</v>
+        <v>-21.02608728613772</v>
       </c>
       <c r="F35">
-        <v>-0.7580454407192094</v>
+        <v>-1.67574362974454</v>
       </c>
       <c r="G35">
-        <v>-1.299969620301647</v>
+        <v>-1.654039086817779</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.970842703994577</v>
       </c>
       <c r="E36">
-        <v>-19.62252752372636</v>
+        <v>-21.07648467336908</v>
       </c>
       <c r="F36">
-        <v>-0.5506995355932576</v>
+        <v>-1.292695847389032</v>
       </c>
       <c r="G36">
-        <v>-1.483022925350108</v>
+        <v>-1.131383399259801</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.788170660115319</v>
       </c>
       <c r="E37">
-        <v>-20.02650816147662</v>
+        <v>-20.71758046589116</v>
       </c>
       <c r="F37">
-        <v>-0.9291466522644142</v>
+        <v>-1.259280444426217</v>
       </c>
       <c r="G37">
-        <v>-1.151485031774256</v>
+        <v>-1.490081008439834</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.577986390781118</v>
       </c>
       <c r="E38">
-        <v>-19.31456412036073</v>
+        <v>-20.2722141041848</v>
       </c>
       <c r="F38">
-        <v>-0.9542032554055394</v>
+        <v>-1.591201448713594</v>
       </c>
       <c r="G38">
-        <v>-1.057008683174535</v>
+        <v>-2.206949850059157</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.365209238865961</v>
       </c>
       <c r="E39">
-        <v>-19.55382151608198</v>
+        <v>-19.88841234661271</v>
       </c>
       <c r="F39">
-        <v>-0.8241532848944406</v>
+        <v>-1.656827054437574</v>
       </c>
       <c r="G39">
-        <v>-0.7869807257183412</v>
+        <v>-0.1812435873068136</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.169069897629341</v>
       </c>
       <c r="E40">
-        <v>-18.65026415427953</v>
+        <v>-19.18131830115903</v>
       </c>
       <c r="F40">
-        <v>-0.5538875356010372</v>
+        <v>-1.250212144354411</v>
       </c>
       <c r="G40">
-        <v>-0.5003238980183884</v>
+        <v>-1.013458456605422</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.002701579183596</v>
       </c>
       <c r="E41">
-        <v>-17.79789213418578</v>
+        <v>-19.10213340466091</v>
       </c>
       <c r="F41">
-        <v>-0.719154374553763</v>
+        <v>-1.496397645203558</v>
       </c>
       <c r="G41">
-        <v>-1.14006696020931</v>
+        <v>-1.389291449496723</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.875622291169114</v>
       </c>
       <c r="E42">
-        <v>-17.97616004197173</v>
+        <v>-17.48026043881377</v>
       </c>
       <c r="F42">
-        <v>-0.6113412188013494</v>
+        <v>-1.570989401967798</v>
       </c>
       <c r="G42">
-        <v>-0.5213723465570747</v>
+        <v>-1.160032860356654</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.788466078331047</v>
       </c>
       <c r="E43">
-        <v>-17.20289140584396</v>
+        <v>-18.03773823152803</v>
       </c>
       <c r="F43">
-        <v>-0.8014556117143624</v>
+        <v>-1.794786844143335</v>
       </c>
       <c r="G43">
-        <v>-0.5273015336179093</v>
+        <v>-1.262805436077789</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.740920707540176</v>
       </c>
       <c r="E44">
-        <v>-16.92372909716712</v>
+        <v>-16.37828798836524</v>
       </c>
       <c r="F44">
-        <v>-1.009376402087619</v>
+        <v>-1.462828622766946</v>
       </c>
       <c r="G44">
-        <v>0.06826560889697723</v>
+        <v>-0.9277848485946234</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.723877734052505</v>
       </c>
       <c r="E45">
-        <v>-16.06297487168516</v>
+        <v>-16.16682636610307</v>
       </c>
       <c r="F45">
-        <v>-0.9101857331918154</v>
+        <v>-1.444287385761938</v>
       </c>
       <c r="G45">
-        <v>-0.6955798739246031</v>
+        <v>-1.197971712236702</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.730766317803531</v>
       </c>
       <c r="E46">
-        <v>-15.3365261283227</v>
+        <v>-16.49170814836136</v>
       </c>
       <c r="F46">
-        <v>-1.032485838805711</v>
+        <v>-1.258495718145117</v>
       </c>
       <c r="G46">
-        <v>-1.066956872520045</v>
+        <v>-1.724712612990141</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.750680708327167</v>
       </c>
       <c r="E47">
-        <v>-14.34777005653994</v>
+        <v>-15.36954323231263</v>
       </c>
       <c r="F47">
-        <v>-1.101498199629859</v>
+        <v>-2.00201001206084</v>
       </c>
       <c r="G47">
-        <v>-1.03722486303185</v>
+        <v>-2.145890148132839</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.776050228974716</v>
       </c>
       <c r="E48">
-        <v>-15.36147802010496</v>
+        <v>-16.04380131273669</v>
       </c>
       <c r="F48">
-        <v>-1.154871464539041</v>
+        <v>-1.312719433130891</v>
       </c>
       <c r="G48">
-        <v>-0.2099989858609231</v>
+        <v>-0.8030434926748851</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.79649940608631</v>
       </c>
       <c r="E49">
-        <v>-14.69876754840046</v>
+        <v>-14.03587140926165</v>
       </c>
       <c r="F49">
-        <v>-0.9867800860861289</v>
+        <v>-1.813074688201872</v>
       </c>
       <c r="G49">
-        <v>-0.8239727615741574</v>
+        <v>-1.970182943636021</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.806417739843815</v>
       </c>
       <c r="E50">
-        <v>-13.99018816347227</v>
+        <v>-13.54276134609241</v>
       </c>
       <c r="F50">
-        <v>-1.187650217723849</v>
+        <v>-1.778785079573735</v>
       </c>
       <c r="G50">
-        <v>-1.101952649415681</v>
+        <v>-2.515459588863838</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.799647422739064</v>
       </c>
       <c r="E51">
-        <v>-13.9302855092988</v>
+        <v>-14.01792506676925</v>
       </c>
       <c r="F51">
-        <v>-1.002157078672088</v>
+        <v>-1.92774133130335</v>
       </c>
       <c r="G51">
-        <v>-0.901313726462611</v>
+        <v>-1.655740707224965</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.775000227332462</v>
       </c>
       <c r="E52">
-        <v>-12.84904441285739</v>
+        <v>-12.48071645096951</v>
       </c>
       <c r="F52">
-        <v>-1.285567587063639</v>
+        <v>-1.765066227081241</v>
       </c>
       <c r="G52">
-        <v>-1.402626326928907</v>
+        <v>-1.681841048256579</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.731520266628018</v>
       </c>
       <c r="E53">
-        <v>-12.93221889495627</v>
+        <v>-12.89038938054742</v>
       </c>
       <c r="F53">
-        <v>-1.468468991384783</v>
+        <v>-1.636278470184747</v>
       </c>
       <c r="G53">
-        <v>-1.526427487915493</v>
+        <v>-2.060560836858124</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.669189909876588</v>
       </c>
       <c r="E54">
-        <v>-11.97626708888507</v>
+        <v>-12.47158704737005</v>
       </c>
       <c r="F54">
-        <v>-1.729131148006962</v>
+        <v>-1.605556159131137</v>
       </c>
       <c r="G54">
-        <v>-1.966978335554006</v>
+        <v>-2.274147303415283</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.591565895923994</v>
       </c>
       <c r="E55">
-        <v>-11.70923203360077</v>
+        <v>-11.96096084673915</v>
       </c>
       <c r="F55">
-        <v>-1.353338322450082</v>
+        <v>-1.928118253311224</v>
       </c>
       <c r="G55">
-        <v>-1.54065621264328</v>
+        <v>-1.589751602990672</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.500232777190901</v>
       </c>
       <c r="E56">
-        <v>-11.6956737824218</v>
+        <v>-11.53730851789956</v>
       </c>
       <c r="F56">
-        <v>-1.464132012735352</v>
+        <v>-1.903586648681067</v>
       </c>
       <c r="G56">
-        <v>-1.536359124533306</v>
+        <v>-1.887535174248115</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.402933021483383</v>
       </c>
       <c r="E57">
-        <v>-11.98597613715752</v>
+        <v>-11.66221288797913</v>
       </c>
       <c r="F57">
-        <v>-1.238104712630877</v>
+        <v>-1.762071439195145</v>
       </c>
       <c r="G57">
-        <v>-2.20761526971255</v>
+        <v>-1.720140749600407</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.302508133991214</v>
       </c>
       <c r="E58">
-        <v>-10.9759905792268</v>
+        <v>-10.36988603261818</v>
       </c>
       <c r="F58">
-        <v>-1.553891712904714</v>
+        <v>-1.765912717893043</v>
       </c>
       <c r="G58">
-        <v>-2.432437727829996</v>
+        <v>-3.726311483125511</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.205761149975473</v>
       </c>
       <c r="E59">
-        <v>-11.48499105768895</v>
+        <v>-11.08082022403036</v>
       </c>
       <c r="F59">
-        <v>-1.53297412517359</v>
+        <v>-1.578730556482466</v>
       </c>
       <c r="G59">
-        <v>-2.224207723955377</v>
+        <v>-3.012481722311239</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.114093495340456</v>
       </c>
       <c r="E60">
-        <v>-11.33914702379792</v>
+        <v>-10.25334575403078</v>
       </c>
       <c r="F60">
-        <v>-1.688691217456215</v>
+        <v>-2.095141422124172</v>
       </c>
       <c r="G60">
-        <v>-2.545201529988651</v>
+        <v>-3.886581613772707</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.029564167937691</v>
       </c>
       <c r="E61">
-        <v>-10.6944327077999</v>
+        <v>-9.574033896614157</v>
       </c>
       <c r="F61">
-        <v>-1.715831977582059</v>
+        <v>-1.684267926834393</v>
       </c>
       <c r="G61">
-        <v>-2.345380311783781</v>
+        <v>-3.487687360654844</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.949383024223764</v>
       </c>
       <c r="E62">
-        <v>-10.73082352492553</v>
+        <v>-11.16538041917559</v>
       </c>
       <c r="F62">
-        <v>-1.710542399824491</v>
+        <v>-2.099456228890787</v>
       </c>
       <c r="G62">
-        <v>-2.765859321817693</v>
+        <v>-3.557629256263026</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.871371896368569</v>
       </c>
       <c r="E63">
-        <v>-10.21091848105292</v>
+        <v>-9.90162370632903</v>
       </c>
       <c r="F63">
-        <v>-1.879931625275106</v>
+        <v>-2.284164641661448</v>
       </c>
       <c r="G63">
-        <v>-2.341808233146907</v>
+        <v>-2.71054672694755</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.790329413776591</v>
       </c>
       <c r="E64">
-        <v>-10.6536990841009</v>
+        <v>-10.14359365798088</v>
       </c>
       <c r="F64">
-        <v>-2.0691567673166</v>
+        <v>-2.061204979915178</v>
       </c>
       <c r="G64">
-        <v>-2.682552753867473</v>
+        <v>-3.816338458520451</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.700947623172224</v>
       </c>
       <c r="E65">
-        <v>-10.45083703397929</v>
+        <v>-9.941519562336605</v>
       </c>
       <c r="F65">
-        <v>-1.738563700439319</v>
+        <v>-2.234662745862557</v>
       </c>
       <c r="G65">
-        <v>-2.626147678969371</v>
+        <v>-3.401510549722075</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.597736686537305</v>
       </c>
       <c r="E66">
-        <v>-10.76592372695899</v>
+        <v>-9.832895056314618</v>
       </c>
       <c r="F66">
-        <v>-2.054110769266967</v>
+        <v>-2.316385138511063</v>
       </c>
       <c r="G66">
-        <v>-2.89987682633847</v>
+        <v>-4.21289215594205</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.474651315217907</v>
       </c>
       <c r="E67">
-        <v>-10.8645855901641</v>
+        <v>-9.64581473810974</v>
       </c>
       <c r="F67">
-        <v>-1.764783535575335</v>
+        <v>-2.446415312698219</v>
       </c>
       <c r="G67">
-        <v>-3.072607850395483</v>
+        <v>-4.245179906586563</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.330252647282161</v>
       </c>
       <c r="E68">
-        <v>-10.45325976757339</v>
+        <v>-9.259169098860836</v>
       </c>
       <c r="F68">
-        <v>-1.808729791022864</v>
+        <v>-2.413669817337635</v>
       </c>
       <c r="G68">
-        <v>-2.82805785140952</v>
+        <v>-4.812994745845739</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.160638165463788</v>
       </c>
       <c r="E69">
-        <v>-10.5476648652113</v>
+        <v>-8.986029660614191</v>
       </c>
       <c r="F69">
-        <v>-1.866474084258659</v>
+        <v>-2.695139494129815</v>
       </c>
       <c r="G69">
-        <v>-3.083128764119287</v>
+        <v>-4.563508723460723</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.968649703674332</v>
       </c>
       <c r="E70">
-        <v>-11.17118592285342</v>
+        <v>-10.53349979851531</v>
       </c>
       <c r="F70">
-        <v>-1.945052028812061</v>
+        <v>-2.814853407983799</v>
       </c>
       <c r="G70">
-        <v>-3.198527760527202</v>
+        <v>-3.901038766142705</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.751773925437583</v>
       </c>
       <c r="E71">
-        <v>-9.753130515143512</v>
+        <v>-9.698680143675283</v>
       </c>
       <c r="F71">
-        <v>-2.511131871226737</v>
+        <v>-2.502889473789832</v>
       </c>
       <c r="G71">
-        <v>-3.042425606713948</v>
+        <v>-4.549015155089793</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.515223870807969</v>
       </c>
       <c r="E72">
-        <v>-11.4663654440954</v>
+        <v>-10.04725037346769</v>
       </c>
       <c r="F72">
-        <v>-2.201916458649015</v>
+        <v>-2.579581224597945</v>
       </c>
       <c r="G72">
-        <v>-3.608631520841038</v>
+        <v>-3.503448867967314</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.259505948879245</v>
       </c>
       <c r="E73">
-        <v>-10.33933694696243</v>
+        <v>-8.864657500260611</v>
       </c>
       <c r="F73">
-        <v>-2.73081880469875</v>
+        <v>-2.71081659898675</v>
       </c>
       <c r="G73">
-        <v>-2.806588963587347</v>
+        <v>-4.510652553380719</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.989891316004968</v>
       </c>
       <c r="E74">
-        <v>-12.12874986567135</v>
+        <v>-9.928930404595283</v>
       </c>
       <c r="F74">
-        <v>-2.396367038358502</v>
+        <v>-2.669798615776869</v>
       </c>
       <c r="G74">
-        <v>-3.563144625131452</v>
+        <v>-4.413524457804042</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.70882026838611</v>
       </c>
       <c r="E75">
-        <v>-11.41985801603663</v>
+        <v>-10.04058898820241</v>
       </c>
       <c r="F75">
-        <v>-2.191458456636411</v>
+        <v>-2.780284275261586</v>
       </c>
       <c r="G75">
-        <v>-2.48474765789602</v>
+        <v>-3.355609835820081</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.421277000640153</v>
       </c>
       <c r="E76">
-        <v>-11.82836712779456</v>
+        <v>-11.4796519868339</v>
       </c>
       <c r="F76">
-        <v>-2.495240966071217</v>
+        <v>-2.709205970070748</v>
       </c>
       <c r="G76">
-        <v>-2.933588111564868</v>
+        <v>-3.979717191429024</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.132204619868681</v>
       </c>
       <c r="E77">
-        <v>-11.95114311509052</v>
+        <v>-11.69269404652476</v>
       </c>
       <c r="F77">
-        <v>-2.851055341504829</v>
+        <v>-2.495025582066718</v>
       </c>
       <c r="G77">
-        <v>-3.081854204086667</v>
+        <v>-4.092739216139742</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.846220703365361</v>
       </c>
       <c r="E78">
-        <v>-12.84927536503178</v>
+        <v>-11.41964970623227</v>
       </c>
       <c r="F78">
-        <v>-2.48495083688565</v>
+        <v>-2.876578346038051</v>
       </c>
       <c r="G78">
-        <v>-2.595465542911405</v>
+        <v>-3.990870419350828</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.569516182043735</v>
       </c>
       <c r="E79">
-        <v>-13.03636926865868</v>
+        <v>-11.53572355199688</v>
       </c>
       <c r="F79">
-        <v>-2.95252496321295</v>
+        <v>-2.775479311514143</v>
       </c>
       <c r="G79">
-        <v>-3.129267837300109</v>
+        <v>-3.085830169279332</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.307323341127404</v>
       </c>
       <c r="E80">
-        <v>-14.69729579434797</v>
+        <v>-12.37074698816725</v>
       </c>
       <c r="F80">
-        <v>-2.456022072781275</v>
+        <v>-2.906048737565506</v>
       </c>
       <c r="G80">
-        <v>-2.886949146007615</v>
+        <v>-3.598531046400721</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.06867996284053</v>
       </c>
       <c r="E81">
-        <v>-14.78177900543507</v>
+        <v>-14.05518082243035</v>
       </c>
       <c r="F81">
-        <v>-2.738814935865804</v>
+        <v>-3.113254484717941</v>
       </c>
       <c r="G81">
-        <v>-2.258461938650216</v>
+        <v>-3.038803869893985</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.8590497127173585</v>
       </c>
       <c r="E82">
-        <v>-15.72414991795726</v>
+        <v>-14.79489346616128</v>
       </c>
       <c r="F82">
-        <v>-2.675237061890487</v>
+        <v>-3.26694601713472</v>
       </c>
       <c r="G82">
-        <v>-2.319614335851634</v>
+        <v>-3.215302294774689</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.6861585548239716</v>
       </c>
       <c r="E83">
-        <v>-16.10404360246073</v>
+        <v>-15.23926356358596</v>
       </c>
       <c r="F83">
-        <v>-2.65853292374739</v>
+        <v>-2.844590653958005</v>
       </c>
       <c r="G83">
-        <v>-2.984166626313853</v>
+        <v>-3.218387723217289</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.5520983112042491</v>
       </c>
       <c r="E84">
-        <v>-17.49373264898659</v>
+        <v>-15.22876656083618</v>
       </c>
       <c r="F84">
-        <v>-2.486557506536863</v>
+        <v>-3.247634307201852</v>
       </c>
       <c r="G84">
-        <v>-2.02101637039153</v>
+        <v>-3.123106912051526</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.4610588156035171</v>
       </c>
       <c r="E85">
-        <v>-18.19574574660367</v>
+        <v>-17.98376334983061</v>
       </c>
       <c r="F85">
-        <v>-3.060792642563094</v>
+        <v>-2.892931693320879</v>
       </c>
       <c r="G85">
-        <v>-2.408899749045778</v>
+        <v>-2.537679970523427</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.4121223383522746</v>
       </c>
       <c r="E86">
-        <v>-19.97997809104781</v>
+        <v>-17.91606266341594</v>
       </c>
       <c r="F86">
-        <v>-2.574605220611634</v>
+        <v>-3.391329487880377</v>
       </c>
       <c r="G86">
-        <v>-1.788725321537488</v>
+        <v>-2.797355852078319</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.4059949258191178</v>
       </c>
       <c r="E87">
-        <v>-20.08022492015561</v>
+        <v>-20.25703013083708</v>
       </c>
       <c r="F87">
-        <v>-2.867770565589335</v>
+        <v>-2.995326199283616</v>
       </c>
       <c r="G87">
-        <v>-2.053615312316733</v>
+        <v>-2.717369761303988</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.4404998777674963</v>
       </c>
       <c r="E88">
-        <v>-22.63339667957619</v>
+        <v>-20.21030986449995</v>
       </c>
       <c r="F88">
-        <v>-2.906747943727173</v>
+        <v>-2.865456771246877</v>
       </c>
       <c r="G88">
-        <v>-1.722752770030892</v>
+        <v>-2.814825600889054</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.5144679622545655</v>
       </c>
       <c r="E89">
-        <v>-24.76751251127497</v>
+        <v>-23.36606301775118</v>
       </c>
       <c r="F89">
-        <v>-2.892348889543997</v>
+        <v>-3.007619716452215</v>
       </c>
       <c r="G89">
-        <v>-1.669274217389505</v>
+        <v>-3.038946223352173</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.6244770143464603</v>
       </c>
       <c r="E90">
-        <v>-25.15098369024449</v>
+        <v>-23.46899976041954</v>
       </c>
       <c r="F90">
-        <v>-2.681468152814784</v>
+        <v>-3.184121365169068</v>
       </c>
       <c r="G90">
-        <v>-1.327185615179996</v>
+        <v>-2.551819310521654</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.7676105001397283</v>
       </c>
       <c r="E91">
-        <v>-28.58315489692393</v>
+        <v>-27.3687177944949</v>
       </c>
       <c r="F91">
-        <v>-2.732035882694766</v>
+        <v>-2.630647029988332</v>
       </c>
       <c r="G91">
-        <v>-1.995607933377623</v>
+        <v>-2.632682695863892</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.9380617462080894</v>
       </c>
       <c r="E92">
-        <v>-29.14798240295263</v>
+        <v>-29.52376876153114</v>
       </c>
       <c r="F92">
-        <v>-2.721542247299064</v>
+        <v>-2.662557912331479</v>
       </c>
       <c r="G92">
-        <v>-2.041435815277755</v>
+        <v>-2.793148148697906</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.132262907228347</v>
       </c>
       <c r="E93">
-        <v>-31.98211880370511</v>
+        <v>-30.78883646760292</v>
       </c>
       <c r="F93">
-        <v>-2.646274248108931</v>
+        <v>-2.993238874887067</v>
       </c>
       <c r="G93">
-        <v>-1.849563216912675</v>
+        <v>-2.811733551355374</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.343160751675338</v>
       </c>
       <c r="E94">
-        <v>-34.37050618669758</v>
+        <v>-32.86187224188624</v>
       </c>
       <c r="F94">
-        <v>-2.865954054904325</v>
+        <v>-3.102341959107606</v>
       </c>
       <c r="G94">
-        <v>-2.682767939327526</v>
+        <v>-2.893583479268315</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.567477494438744</v>
       </c>
       <c r="E95">
-        <v>-36.22706505375523</v>
+        <v>-34.86640578985553</v>
       </c>
       <c r="F95">
-        <v>-2.686877300368967</v>
+        <v>-3.07675085522002</v>
       </c>
       <c r="G95">
-        <v>-2.576492806425842</v>
+        <v>-2.878196063601782</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.798030447571493</v>
       </c>
       <c r="E96">
-        <v>-38.62243534366752</v>
+        <v>-36.34295776055953</v>
       </c>
       <c r="F96">
-        <v>-2.60209597974479</v>
+        <v>-3.0180705917882</v>
       </c>
       <c r="G96">
-        <v>-2.57636700569535</v>
+        <v>-3.319428883621386</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.028470043992644</v>
       </c>
       <c r="E97">
-        <v>-40.96508513918251</v>
+        <v>-39.17811986067474</v>
       </c>
       <c r="F97">
-        <v>-2.942540489269062</v>
+        <v>-3.277447571059999</v>
       </c>
       <c r="G97">
-        <v>-3.455853154749212</v>
+        <v>-4.288518258241162</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.253262583217178</v>
       </c>
       <c r="E98">
-        <v>-43.28596203166863</v>
+        <v>-40.86078759007486</v>
       </c>
       <c r="F98">
-        <v>-2.850550931170762</v>
+        <v>-3.287173109086713</v>
       </c>
       <c r="G98">
-        <v>-3.105769585062363</v>
+        <v>-3.816126583605938</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.462151601736184</v>
       </c>
       <c r="E99">
-        <v>-45.4175917311372</v>
+        <v>-45.17425644457204</v>
       </c>
       <c r="F99">
-        <v>-3.220427823280517</v>
+        <v>-3.107578482717007</v>
       </c>
       <c r="G99">
-        <v>-3.814060803189433</v>
+        <v>-4.355685916687435</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.654258063194986</v>
       </c>
       <c r="E100">
-        <v>-48.49975491752679</v>
+        <v>-47.40880930128694</v>
       </c>
       <c r="F100">
-        <v>-3.049220503438978</v>
+        <v>-3.158705260785138</v>
       </c>
       <c r="G100">
-        <v>-4.035542920857754</v>
+        <v>-5.112569322239928</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.810433257553745</v>
       </c>
       <c r="E101">
-        <v>-49.59874423572276</v>
+        <v>-48.64710353690686</v>
       </c>
       <c r="F101">
-        <v>-2.841530142276418</v>
+        <v>-3.311486162300539</v>
       </c>
       <c r="G101">
-        <v>-4.772457115717363</v>
+        <v>-4.529708053504764</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.938866117945055</v>
       </c>
       <c r="E102">
-        <v>-51.50678845589211</v>
+        <v>-50.30247022863323</v>
       </c>
       <c r="F102">
-        <v>-3.326453766907358</v>
+        <v>-3.100783592486814</v>
       </c>
       <c r="G102">
-        <v>-4.570841581830209</v>
+        <v>-4.477864910359777</v>
       </c>
     </row>
   </sheetData>
